--- a/inputs/tuning.xlsx
+++ b/inputs/tuning.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -531,323 +531,338 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>top_summary_size</t>
+          <t>target_digest_min</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Stories promoted into 'Today's biggest stories' at the top of the Slack post.</t>
+          <t>Floor on total ranked stories. If normal S/A selection lands below this, the ranker backfills with the best remaining Tier-B stories so slow news days aren't thin. 0 disables the floor.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dedup_window_days</t>
+          <t>top_summary_size</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How far back 'recently sent' goes for URL dedup, ranker candidate filter, and cross-day similarity.</t>
+          <t>Stories promoted into 'Today's biggest stories' at the top of the Slack post.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>historical_dedup_threshold</t>
+          <t>dedup_window_days</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8</v>
+        <v>30</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cosine similarity above which a new story is dropped as a duplicate of one sent in the last N days.</t>
+          <t>How far back 'recently sent' goes for URL dedup, ranker candidate filter, and cross-day similarity.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cluster_similarity_threshold</t>
+          <t>historical_dedup_threshold</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Within-day clustering threshold. Signals above this collapse into one story.</t>
+          <t>Cosine similarity above which a new story is dropped as a duplicate of one sent in the last N days.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>top_k_content_similarity</t>
+          <t>cluster_similarity_threshold</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>0.85</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How many content corpus chunks to compare against per story. More = smoother score, slower.</t>
+          <t>Within-day clustering threshold. Signals above this collapse into one story.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>summary_truncate_for_embed</t>
+          <t>top_k_content_similarity</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>400</v>
+        <v>5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Characters of summary text fed to the embedding model.</t>
+          <t>How many content corpus chunks to compare against per story. More = smoother score, slower.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>min_candidate_score</t>
+          <t>summary_truncate_for_embed</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3</v>
+        <v>400</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pre-filter on relevance_score before ranker sees stories. 0.3 drops non-healthcare (near-zero content-similarity) stories; healthcare stories typically score 0.5-0.7. 0.0 = no pre-filter.</t>
+          <t>Characters of summary text fed to the embedding model.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>one_liner_max_chars</t>
+          <t>min_candidate_score</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>120</v>
+        <v>0.3</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hard cap on the one-line headline. Forces newsroom-punchy output.</t>
+          <t>Pre-filter on relevance_score before ranker sees stories. 0.3 drops non-healthcare (near-zero content-similarity) stories; healthcare stories typically score 0.5-0.7. 0.0 = no pre-filter.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ranker_summary_max_chars</t>
+          <t>one_liner_max_chars</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How much of each story's summary the prompt shows the ranker.</t>
+          <t>Hard cap on the one-line headline. Forces newsroom-punchy output.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>perplexity_model_fetch</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>sonar-pro</t>
-        </is>
+          <t>ranker_summary_max_chars</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>220</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Model for the 30+-plan fetch sweep.</t>
+          <t>How much of each story's summary the prompt shows the ranker.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>perplexity_model_rank</t>
+          <t>perplexity_model_fetch</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sonar-reasoning-pro</t>
+          <t>sonar-pro</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Model for the single ranking call.</t>
+          <t>Model for the 30+-plan fetch sweep.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>perplexity_recency</t>
+          <t>perplexity_model_rank</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>day</t>
+          <t>sonar-reasoning-pro</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Recency filter on the fetch sweep.</t>
+          <t>Model for the single ranking call.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>embedding_model</t>
+          <t>perplexity_recency</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>text-embedding-3-small</t>
+          <t>day</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Embedding model for both content-corpus indexing and signal embedding. Switching requires re-indexing.</t>
+          <t>Recency filter on the fetch sweep.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>http_timeout_s</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>30</v>
+          <t>embedding_model</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>text-embedding-3-small</t>
+        </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Default timeout in seconds for fetch HTTP calls.</t>
+          <t>Embedding model for both content-corpus indexing and signal embedding. Switching requires re-indexing.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>http_timeout_rank_s</t>
+          <t>http_timeout_s</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Looser timeout in seconds for sonar-reasoning-pro (extended chain-of-thought).</t>
+          <t>Default timeout in seconds for fetch HTTP calls.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>http_max_retries</t>
+          <t>http_timeout_rank_s</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Max retries on retryable HTTP errors.</t>
+          <t>Looser timeout in seconds for sonar-reasoning-pro (extended chain-of-thought).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>url_validation_timeout_s</t>
+          <t>http_max_retries</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HEAD validation budget per story before posting to Slack.</t>
+          <t>Max retries on retryable HTTP errors.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>digest_tz</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Asia/Kolkata</t>
-        </is>
+          <t>url_validation_timeout_s</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>10</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Intended fire timezone (the actual cron is in .github/workflows/daily-digest.yml).</t>
+          <t>HEAD validation budget per story before posting to Slack.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>digest_hour_local</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>10</v>
+          <t>digest_tz</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Asia/Kolkata</t>
+        </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Intended fire hour, local time.</t>
+          <t>Intended fire timezone (the actual cron is in .github/workflows/daily-digest.yml).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>track_b_plans_per_day</t>
+          <t>digest_hour_local</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Non-priority sub-buckets sampled per day from the rotation.</t>
+          <t>Intended fire hour, local time.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>track_b_plans_per_day</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>18</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Non-priority sub-buckets sampled per day from the rotation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>track_b_rotation_days</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B26" t="n">
         <v>14</v>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Full-cycle length of the Track B rotation.</t>
         </is>

--- a/inputs/tuning.xlsx
+++ b/inputs/tuning.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -490,11 +490,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hard cap on Perplexity API calls per day across fetch + ranker.</t>
+          <t>Hard cap on Perplexity calls/day (fetch only; the ranker now runs on Claude, not Perplexity).</t>
         </is>
       </c>
     </row>
@@ -640,11 +640,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pre-filter on relevance_score before ranker sees stories. 0.3 drops non-healthcare (near-zero content-similarity) stories; healthcare stories typically score 0.5-0.7. 0.0 = no pre-filter.</t>
+          <t>Deprecated as a gate. Relevance no longer filters candidates; topicality (is_healthcare) does. 0.0 = no score pre-filter.</t>
         </is>
       </c>
     </row>
@@ -670,11 +670,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>220</v>
+        <v>400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How much of each story's summary the prompt shows the ranker.</t>
+          <t>How much of each story's summary the ranker reads when writing the one-liner. 300-400 gives accurate, precise headlines.</t>
         </is>
       </c>
     </row>
@@ -830,11 +830,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Intended fire hour, local time.</t>
+          <t>Intended fire hour, local time (IST). Digest holds until this hour before posting.</t>
         </is>
       </c>
     </row>
@@ -845,11 +845,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Non-priority sub-buckets sampled per day from the rotation.</t>
+          <t>Safety cap on Track B plans/day. Actual count is derived from track_b_rotation_days (ceil of non-priority subs / rotation days) but never exceeds this, protecting the Perplexity budget.</t>
         </is>
       </c>
     </row>
@@ -860,11 +860,75 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Full-cycle length of the Track B rotation.</t>
+          <t>Full-cycle length of the Track B rotation. Plans/day is derived: ceil(non-priority subs / this).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ranker_provider</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Which vendor runs the single ranking call: 'anthropic' (Claude) or 'perplexity'. Falls back to perplexity automatically if ANTHROPIC_API_KEY is unset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>anthropic_model_rank</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-5</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Claude model for the ranking/tiering/one-liner call. Change here without code edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>anthropic_max_tokens_rank</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4096</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Max output tokens for the Claude ranking call (must fit the JSON tier+one_liner+bucket list for the whole candidate pool).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>per_bucket_max</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Max stories shown per priority bucket in the digest body (each bucket shows 1-2). Keeps the digest uniform; no bucket dominates.</t>
         </is>
       </c>
     </row>
